--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487898_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487898_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1871</v>
+        <v>4.3414</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4941</v>
+        <v>4.0888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.2526</v>
       </c>
       <c r="G2" t="n">
         <v>4.2423</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7504</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8539</v>
+        <v>0.4487</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8965</v>
+        <v>0.4561</v>
       </c>
       <c r="V2" t="n">
         <v>-1.6381</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.47</v>
+        <v>4.1378</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0286</v>
+        <v>2.3734</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4414</v>
+        <v>1.7643</v>
       </c>
       <c r="G3" t="n">
         <v>0.9538</v>
@@ -688,13 +688,13 @@
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2538</v>
+        <v>0.414</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1396</v>
+        <v>0.4844</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3934</v>
+        <v>-0.0704</v>
       </c>
       <c r="V3" t="n">
         <v>1.5213</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.366</v>
+        <v>3.5655</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1424</v>
+        <v>1.1658</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2235</v>
+        <v>2.3997</v>
       </c>
       <c r="G4" t="n">
         <v>6.1767</v>
@@ -766,13 +766,13 @@
         <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1559</v>
+        <v>0.0436</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0091</v>
+        <v>0.0324</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.165</v>
+        <v>0.0111</v>
       </c>
       <c r="V4" t="n">
         <v>0.467</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7532</v>
+        <v>3.2932</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6276</v>
+        <v>2.0796</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1256</v>
+        <v>1.2137</v>
       </c>
       <c r="G5" t="n">
         <v>1.8155</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3321</v>
+        <v>0.8721</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4782</v>
+        <v>0.9301</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1461</v>
+        <v>-0.058</v>
       </c>
       <c r="V5" t="n">
         <v>0.8137</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.38</v>
+        <v>3.1631</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3493</v>
+        <v>2.3996</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0306</v>
+        <v>0.7635</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8091</v>
+        <v>1.8672</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9062</v>
+        <v>0.516</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09710000000000001</v>
+        <v>1.3512</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9928</v>
+        <v>2.8104</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9144</v>
+        <v>1.1041</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0784</v>
+        <v>1.7063</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8163</v>
+        <v>-0.9432</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9918</v>
+        <v>-0.5881</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1755</v>
+        <v>-0.3551</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0406</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7055</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5927</v>
+        <v>0.2857</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0621</v>
+        <v>-0.0809</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5307</v>
+        <v>0.3667</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.9813</v>
+        <v>1.6345</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.9813</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3169</v>
+        <v>2.5967</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9057</v>
+        <v>0.0415</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4112</v>
+        <v>2.5553</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8672</v>
+        <v>-0.1842</v>
       </c>
       <c r="H7" t="n">
-        <v>0.516</v>
+        <v>4.2473</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3512</v>
+        <v>-4.4316</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8104</v>
+        <v>-0.1881</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1041</v>
+        <v>4.0679</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7063</v>
+        <v>-4.256</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9432</v>
+        <v>0.0039</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5881</v>
+        <v>0.1794</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3551</v>
+        <v>-0.1755</v>
       </c>
       <c r="P7" t="n">
+        <v>1.0406</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.6244</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5604</v>
+        <v>1.0327</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5748</v>
+        <v>0.8539</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0144</v>
+        <v>0.1788</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6345</v>
+        <v>0.7076</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1168</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1204</v>
+        <v>1.8873</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0238</v>
+        <v>2.9256</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1442</v>
+        <v>-1.0382</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1842</v>
+        <v>3.2785</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2473</v>
+        <v>2.4073</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.4316</v>
+        <v>0.8711</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1881</v>
+        <v>3.6542</v>
       </c>
       <c r="K8" t="n">
-        <v>4.0679</v>
+        <v>2.3218</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.256</v>
+        <v>1.3324</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0039</v>
+        <v>-0.3757</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1794</v>
+        <v>0.0856</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1755</v>
+        <v>-0.4613</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6244</v>
+        <v>-1.2487</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5565</v>
+        <v>0.6663</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7887</v>
+        <v>0.5201</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2322</v>
+        <v>0.1462</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7076</v>
+        <v>-2.6818</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7076</v>
+        <v>-2.6818</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9348</v>
+        <v>1.6455</v>
       </c>
       <c r="E9" t="n">
-        <v>0.95</v>
+        <v>0.8662</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9848</v>
+        <v>0.7793</v>
       </c>
       <c r="G9" t="n">
         <v>2.2656</v>
@@ -1156,13 +1156,13 @@
         <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9317</v>
+        <v>0.6423</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4129</v>
+        <v>0.3291</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5187</v>
+        <v>0.3132</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0543</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.9215</v>
+        <v>1.5223</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3429</v>
+        <v>0.9142</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5787</v>
+        <v>0.608</v>
       </c>
       <c r="G10" t="n">
         <v>1.0447</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6687</v>
+        <v>0.2694</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6491</v>
+        <v>0.2205</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7149</v>
+        <v>1.4088</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7532</v>
+        <v>0.2002</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0382</v>
+        <v>1.2086</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2785</v>
+        <v>2.8091</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4073</v>
+        <v>2.9062</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8711</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6542</v>
+        <v>1.9928</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3218</v>
+        <v>1.9144</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3324</v>
+        <v>0.0784</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3757</v>
+        <v>0.8163</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0856</v>
+        <v>0.9918</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4613</v>
+        <v>-0.1755</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6244</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2487</v>
+        <v>-2.7055</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4939</v>
+        <v>1.6216</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3477</v>
+        <v>0.913</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1462</v>
+        <v>0.7086</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6818</v>
+        <v>-1.9813</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6818</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3302</v>
+        <v>1.0025</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0352</v>
+        <v>-0.3923</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3654</v>
+        <v>1.3948</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7923</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06</v>
+        <v>0.7323</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.171</v>
+        <v>0.472</v>
       </c>
       <c r="U12" t="n">
-        <v>0.231</v>
+        <v>0.2604</v>
       </c>
       <c r="V12" t="n">
         <v>0.23</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4749</v>
+        <v>-1.5653</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4242</v>
+        <v>-2.5732</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9492</v>
+        <v>1.008</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3713</v>
@@ -1468,13 +1468,13 @@
         <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4802</v>
+        <v>0.3898</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5839</v>
+        <v>0.4348</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.0201</v>
+        <v>26.9988</v>
       </c>
       <c r="E14" t="n">
-        <v>13.1106</v>
+        <v>14.0894</v>
       </c>
       <c r="F14" t="n">
-        <v>12.9094</v>
+        <v>12.9096</v>
       </c>
       <c r="G14" t="n">
         <v>21.1056</v>
@@ -1528,13 +1528,13 @@
         <v>3.878</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1204</v>
+        <v>0.1204000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.09979999999999972</v>
+        <v>0.09980000000000017</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02049999999999993</v>
+        <v>0.02050000000000005</v>
       </c>
       <c r="P14" t="n">
         <v>1.110223024625157e-16</v>
@@ -1546,16 +1546,16 @@
         <v>17.69</v>
       </c>
       <c r="S14" t="n">
-        <v>6.8961</v>
+        <v>7.8745</v>
       </c>
       <c r="T14" t="n">
-        <v>4.579400000000001</v>
+        <v>5.5581</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3167</v>
+        <v>2.3166</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.9814</v>
+        <v>-1.981399999999999</v>
       </c>
       <c r="W14" t="n">
         <v>5.2363</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3183</v>
+        <v>0.0297</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1806</v>
+        <v>1.9663</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4989</v>
+        <v>-1.9366</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1274</v>
+        <v>-1.1448</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2794</v>
+        <v>-1.6608</v>
       </c>
       <c r="I15" t="n">
-        <v>1.152</v>
+        <v>0.516</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3508</v>
+        <v>2.0151</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2724</v>
+        <v>0.2214</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0784</v>
+        <v>1.7937</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4782</v>
+        <v>-3.1599</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.5518</v>
+        <v>-1.8823</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0736</v>
+        <v>-1.2777</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8325</v>
+        <v>0.8325</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4974</v>
+        <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0045</v>
+        <v>-1.0555</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8787</v>
+        <v>-0.1976</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8742</v>
+        <v>-0.8579</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2737</v>
+        <v>1.3975</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9199000000000001</v>
+        <v>1.3975</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5735</v>
+        <v>0.0008</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2925</v>
+        <v>-0.9306</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.281</v>
+        <v>0.9314</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.03</v>
+        <v>-0.1274</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8316</v>
+        <v>-1.2794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1984</v>
+        <v>1.152</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0565</v>
+        <v>1.3508</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8672</v>
+        <v>1.2724</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8107</v>
+        <v>0.0784</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0865</v>
+        <v>-1.4782</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.6988</v>
+        <v>-2.5518</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6123</v>
+        <v>1.0736</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2081</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2893</v>
+        <v>-3.3299</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0812</v>
+        <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.503</v>
+        <v>-0.313</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8110000000000001</v>
+        <v>0.1286</v>
       </c>
       <c r="U16" t="n">
-        <v>0.308</v>
+        <v>-0.4416</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1675</v>
+        <v>1.2737</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7513</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5838</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0561</v>
+        <v>-0.6606</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4305</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4866</v>
+        <v>-0.5824</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1448</v>
+        <v>-1.03</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6608</v>
+        <v>-0.8316</v>
       </c>
       <c r="I17" t="n">
-        <v>0.516</v>
+        <v>-0.1984</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0151</v>
+        <v>1.0565</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2214</v>
+        <v>1.8672</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7937</v>
+        <v>-0.8107</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1599</v>
+        <v>-2.0865</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8823</v>
+        <v>-2.6988</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2777</v>
+        <v>0.6123</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="R17" t="n">
         <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1412</v>
+        <v>-0.5901</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.5967</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4079</v>
+        <v>0.0066</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3975</v>
+        <v>1.7513</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5371</v>
+        <v>-1.0935</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4081</v>
+        <v>-0.7192</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1289</v>
+        <v>-0.3743</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9286</v>
+        <v>-1.9452</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8721</v>
+        <v>-0.6332</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0564</v>
+        <v>-1.312</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4913</v>
+        <v>-0.104</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5697</v>
+        <v>0.5712</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0784</v>
+        <v>-0.6752</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4373</v>
+        <v>-1.8412</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3025</v>
+        <v>-1.2044</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1348</v>
+        <v>-0.6368</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2487</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3379</v>
+        <v>-0.7914</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0438</v>
+        <v>-0.4071</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2942</v>
+        <v>-0.3842</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5213</v>
+        <v>-0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3538</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TSEGAKELE</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5832</v>
+        <v>-1.7847</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0173</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5659</v>
+        <v>-1.1622</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5288</v>
+        <v>-2.9286</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4267</v>
+        <v>-1.8721</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1022</v>
+        <v>-1.0564</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8959</v>
+        <v>-0.4913</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8959</v>
+        <v>-0.5697</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6329</v>
+        <v>-2.4373</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5308</v>
+        <v>-1.3025</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1022</v>
+        <v>-1.1348</v>
       </c>
       <c r="P19" t="n">
         <v>0.2081</v>
@@ -1936,28 +1936,28 @@
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9675</v>
+        <v>-0.5855</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9192</v>
+        <v>-0.2581</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0483</v>
+        <v>-0.3275</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.23</v>
+        <v>1.5213</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.23</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>A. TSEGAKELE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8959</v>
+        <v>-2.3372</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1478</v>
+        <v>-1.7674</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7481</v>
+        <v>-0.5698</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9452</v>
+        <v>-2.5288</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6332</v>
+        <v>-1.4267</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.312</v>
+        <v>-1.1022</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.104</v>
+        <v>-0.8959</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5712</v>
+        <v>-0.8959</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6752</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8412</v>
+        <v>-1.6329</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2044</v>
+        <v>-0.5308</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6368</v>
+        <v>-1.1022</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0812</v>
+        <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5938</v>
+        <v>0.2135</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8358</v>
+        <v>0.1691</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7581</v>
+        <v>0.0444</v>
       </c>
       <c r="V20" t="n">
         <v>-0.23</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1502</v>
+        <v>-2.9192</v>
       </c>
       <c r="E21" t="n">
         <v>-2.9839</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1662</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5904</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2923</v>
+        <v>-0.0613</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1618</v>
+        <v>0.0692</v>
       </c>
       <c r="V21" t="n">
         <v>0.23</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2576</v>
+        <v>-3.6655</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9658</v>
+        <v>-1.7515</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2917</v>
+        <v>-1.914</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9725</v>
@@ -2170,13 +2170,13 @@
         <v>2.0812</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4307</v>
+        <v>-0.8387</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6805</v>
+        <v>-0.4662</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7502</v>
+        <v>-0.3725</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8137</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8151</v>
+        <v>-4.8318</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5824</v>
+        <v>-2.7967</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2327</v>
+        <v>-2.0351</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2379</v>
@@ -2248,13 +2248,13 @@
         <v>2.0812</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4097</v>
+        <v>-0.4264</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.109</v>
+        <v>-0.3233</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3007</v>
+        <v>-0.103</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.47</v>
+        <v>-6.6151</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7615</v>
+        <v>-3.2258</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.7084</v>
+        <v>-3.3894</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5999</v>
@@ -2326,13 +2326,13 @@
         <v>1.6649</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1593</v>
+        <v>-0.3045</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7705</v>
+        <v>-0.2347</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3888</v>
+        <v>-0.0698</v>
       </c>
       <c r="V24" t="n">
         <v>-2.3351</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.0204</v>
+        <v>-23.8771</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.9094</v>
+        <v>-12.9095</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.1106</v>
+        <v>-10.9677</v>
       </c>
       <c r="G25" t="n">
         <v>-21.1055</v>
@@ -2383,7 +2383,7 @@
         <v>-0.1000000000000003</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.02029999999999932</v>
+        <v>-0.02029999999999976</v>
       </c>
       <c r="M25" t="n">
         <v>-20.9852</v>
@@ -2404,13 +2404,13 @@
         <v>17.6901</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.8959</v>
+        <v>-4.7529</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.3166</v>
+        <v>-2.3165</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.5796</v>
+        <v>-2.4363</v>
       </c>
       <c r="V25" t="n">
         <v>1.9812</v>
